--- a/lg-com-status-dashboard/신호등-Article.xlsx
+++ b/lg-com-status-dashboard/신호등-Article.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="396">
   <si>
     <t>Title</t>
   </si>
@@ -844,6 +844,9 @@
     <t>https://www.lg.com/vn/lg-experience/goi-y-va-meo/lam-tuong-va-su-that-ve-may-giat-cua-tren/</t>
   </si>
   <si>
+    <t>https://www.lg.com/au/lg-experience/helpful-hints/top-load-washing-machine-myths-and-truths/</t>
+  </si>
+  <si>
     <t>https://www.lg.com/mx/lg-experience/helpful-hints/mitos-y-verdades-sobre-las-lavadoras-de-carga-superior/</t>
   </si>
   <si>
@@ -878,6 +881,15 @@
     <t>https://www.lg.com/in/magazine/lg-experience-2026-washtower-myths-and-truths/</t>
   </si>
   <si>
+    <t>https://www.lg.com/ee/appliances/tips-and-guides/washtower-myths-and-truths</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/appliances/tips-and-guides/washtower-myths-and-truths</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lv/appliances/tips-and-guides/washtower-myths-and-truths</t>
+  </si>
+  <si>
     <t>Twin Tub Washing Machine Myths and Truths</t>
   </si>
   <si>
@@ -897,6 +909,9 @@
   </si>
   <si>
     <t>https://www.lg.com/my/lg-experience/helpful-hints/understanding-vaccum-suction-power/</t>
+  </si>
+  <si>
+    <t>*</t>
   </si>
   <si>
     <t>How to Stop Your Cordless Vacuum From Smelling Bad</t>
@@ -971,6 +986,15 @@
     <t>https://www.lg.com/in/magazine/how-to-clean-a-microwave-without-harsh-chemicals/</t>
   </si>
   <si>
+    <t>https://www.lg.com/ee/appliances/tips-and-guides/how-to-clean-a-microwave-without-harsh-chemicals</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/appliances/tips-and-guides/how-to-clean-a-microwave-without-harsh-chemicals</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lv/appliances/tips-and-guides/how-to-clean-a-microwave-without-harsh-chemicals</t>
+  </si>
+  <si>
     <t>MWO buying guide</t>
   </si>
   <si>
@@ -996,6 +1020,15 @@
   </si>
   <si>
     <t>https://www.lg.com/id/lg-experience/tips/panduan-ukuran-pembelian-microwave/</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/ee/appliances/tips-and-guides/microwave-size-and-buying-guide</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/appliances/tips-and-guides/microwave-size-and-buying-guide</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lv/appliances/tips-and-guides/microwave-size-and-buying-guide</t>
   </si>
   <si>
     <t>DW</t>
@@ -1049,10 +1082,22 @@
     <t>https://www.lg.com/in/magazine/how-much-water-and-energy-does-a-dishwasher-use/</t>
   </si>
   <si>
+    <t>https://www.lg.com/za/home-appliances/faq/dishwasher/how-much-water-and-energy-does-a-dishwasher-use/</t>
+  </si>
+  <si>
     <t>https://www.lg.com/ae/appliances/tips-and-guides/how-much-water-and-energy-does-a-dishwasher-use</t>
   </si>
   <si>
     <t>https://www.lg.com/ae_ar/appliances/tips-and-guides/how-much-water-and-energy-does-a-dishwasher-use</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/ee/appliances/tips-and-guides/how-much-water-and-energy-does-a-dishwasher-use</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/appliances/tips-and-guides/how-much-water-and-energy-does-a-dishwasher-use</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lv/appliances/tips-and-guides/how-much-water-and-energy-does-a-dishwasher-use</t>
   </si>
   <si>
     <t>integrated dishwashers vs freestanding dishwashers</t>
@@ -1092,6 +1137,15 @@
   </si>
   <si>
     <t>https://www.lg.com/ae_ar/appliances/tips-and-guides/integrated-dishwashers-vs-freestanding-dishwashers</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/ee/appliances/tips-and-guides/integrated-dishwashers-vs-freestanding-dishwashers</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/appliances/tips-and-guides/integrated-dishwashers-vs-freestanding-dishwashers</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lv/appliances/tips-and-guides/integrated-dishwashers-vs-freestanding-dishwashers</t>
   </si>
   <si>
     <t>Ultimate guide to dishwasher maintenance</t>
@@ -1138,6 +1192,15 @@
   </si>
   <si>
     <t>https://www.lg.com/ae_ar/appliances/tips-and-guides/ultimate-guide-to-dishwasher-maintenance</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/ee/appliances/tips-and-guides/the-ultimate-guide-to-dishwasher-maintenance</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lt/appliances/tips-and-guides/the-ultimate-guide-to-dishwasher-maintenance</t>
+  </si>
+  <si>
+    <t>https://www.lg.com/lv/appliances/tips-and-guides/the-ultimate-guide-to-dishwasher-maintenance</t>
   </si>
 </sst>
 </file>
@@ -5495,8 +5558,8 @@
       <c r="M61" s="46" t="s">
         <v>276</v>
       </c>
-      <c r="N61" s="14" t="s">
-        <v>55</v>
+      <c r="N61" s="12" t="s">
+        <v>277</v>
       </c>
       <c r="O61" s="16"/>
       <c r="P61" s="16"/>
@@ -5510,10 +5573,10 @@
       <c r="T61" s="16"/>
       <c r="U61" s="16"/>
       <c r="V61" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="W61" s="73" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="X61" s="16"/>
       <c r="Y61" s="16"/>
@@ -5522,16 +5585,16 @@
       </c>
       <c r="AA61" s="16"/>
       <c r="AB61" s="48" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AC61" s="48" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AD61" s="14" t="s">
         <v>57</v>
       </c>
       <c r="AE61" s="12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AF61" s="14" t="s">
         <v>57</v>
@@ -5551,7 +5614,7 @@
         <v>153</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D62" s="16"/>
       <c r="E62" s="16"/>
@@ -5597,7 +5660,7 @@
         <v>153</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D63" s="74" t="s">
         <v>55</v>
@@ -5624,7 +5687,7 @@
         <v>57</v>
       </c>
       <c r="N63" s="75" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O63" s="64"/>
       <c r="P63" s="64"/>
@@ -5650,23 +5713,29 @@
       </c>
       <c r="AA63" s="64"/>
       <c r="AB63" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AC63" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AD63" s="74" t="s">
         <v>55</v>
       </c>
       <c r="AE63" s="77" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF63" s="64"/>
       <c r="AG63" s="78"/>
       <c r="AH63" s="78"/>
-      <c r="AI63" s="9"/>
-      <c r="AJ63" s="9"/>
-      <c r="AK63" s="9"/>
+      <c r="AI63" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="AJ63" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="AK63" s="19" t="s">
+        <v>291</v>
+      </c>
       <c r="AL63" s="9"/>
       <c r="AM63" s="9"/>
       <c r="AN63" s="9"/>
@@ -5677,7 +5746,7 @@
         <v>153</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
@@ -5726,10 +5795,10 @@
     <row r="65">
       <c r="A65" s="10"/>
       <c r="B65" s="10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D65" s="16"/>
       <c r="E65" s="53"/>
@@ -5746,18 +5815,20 @@
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>
       <c r="N65" s="12" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="O65" s="12" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P65" s="12" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q65" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="R65" s="10"/>
+        <v>298</v>
+      </c>
+      <c r="R65" s="10" t="s">
+        <v>299</v>
+      </c>
       <c r="S65" s="16"/>
       <c r="T65" s="16"/>
       <c r="U65" s="16"/>
@@ -5784,10 +5855,10 @@
     <row r="66">
       <c r="A66" s="10"/>
       <c r="B66" s="10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
@@ -5802,18 +5873,20 @@
       <c r="L66" s="9"/>
       <c r="M66" s="79"/>
       <c r="N66" s="19" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="O66" s="19" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="P66" s="19" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q66" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="R66" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="R66" s="18"/>
       <c r="S66" s="9"/>
       <c r="T66" s="9"/>
       <c r="U66" s="9"/>
@@ -5824,12 +5897,14 @@
       <c r="Z66" s="9"/>
       <c r="AA66" s="9"/>
       <c r="AB66" s="19" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="AC66" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="AD66" s="18"/>
+        <v>306</v>
+      </c>
+      <c r="AD66" s="18" t="s">
+        <v>299</v>
+      </c>
       <c r="AE66" s="9"/>
       <c r="AF66" s="9"/>
       <c r="AG66" s="9"/>
@@ -5844,10 +5919,10 @@
     <row r="67">
       <c r="A67" s="10"/>
       <c r="B67" s="10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
@@ -5862,18 +5937,20 @@
       <c r="L67" s="16"/>
       <c r="M67" s="81"/>
       <c r="N67" s="12" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="O67" s="12" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="P67" s="12" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="R67" s="14"/>
+        <v>311</v>
+      </c>
+      <c r="R67" s="14" t="s">
+        <v>299</v>
+      </c>
       <c r="S67" s="14"/>
       <c r="T67" s="16"/>
       <c r="U67" s="16"/>
@@ -5900,10 +5977,10 @@
     <row r="68">
       <c r="A68" s="10"/>
       <c r="B68" s="10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
@@ -5958,13 +6035,13 @@
     <row r="69">
       <c r="A69" s="10"/>
       <c r="B69" s="84" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C69" s="84" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E69" s="13" t="s">
         <v>56</v>
@@ -5985,7 +6062,7 @@
       </c>
       <c r="L69" s="16"/>
       <c r="M69" s="15" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="N69" s="10" t="s">
         <v>56</v>
@@ -6002,35 +6079,43 @@
       <c r="T69" s="16"/>
       <c r="U69" s="16"/>
       <c r="V69" s="15" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="W69" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="X69" s="10"/>
+        <v>318</v>
+      </c>
+      <c r="X69" s="10" t="s">
+        <v>299</v>
+      </c>
       <c r="Y69" s="16"/>
       <c r="Z69" s="87" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AA69" s="16"/>
       <c r="AB69" s="15" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AC69" s="15" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AD69" s="15" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AE69" s="15" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="AF69" s="10"/>
       <c r="AG69" s="9"/>
       <c r="AH69" s="9"/>
-      <c r="AI69" s="9"/>
-      <c r="AJ69" s="9"/>
-      <c r="AK69" s="9"/>
+      <c r="AI69" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="AJ69" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="AK69" s="19" t="s">
+        <v>326</v>
+      </c>
       <c r="AL69" s="9"/>
       <c r="AM69" s="9"/>
       <c r="AN69" s="9"/>
@@ -6038,13 +6123,13 @@
     <row r="70">
       <c r="A70" s="10"/>
       <c r="B70" s="84" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C70" s="84" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="D70" s="88" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="E70" s="89" t="s">
         <v>56</v>
@@ -6065,7 +6150,7 @@
       </c>
       <c r="L70" s="16"/>
       <c r="M70" s="15" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="N70" s="10" t="s">
         <v>56</v>
@@ -6082,25 +6167,27 @@
       <c r="T70" s="16"/>
       <c r="U70" s="16"/>
       <c r="V70" s="15" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="W70" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="X70" s="10"/>
+        <v>331</v>
+      </c>
+      <c r="X70" s="10" t="s">
+        <v>299</v>
+      </c>
       <c r="Y70" s="16"/>
       <c r="Z70" s="15" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="AA70" s="28"/>
       <c r="AB70" s="15" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="AC70" s="15" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="AD70" s="15" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AE70" s="10" t="s">
         <v>56</v>
@@ -6108,9 +6195,15 @@
       <c r="AF70" s="10"/>
       <c r="AG70" s="9"/>
       <c r="AH70" s="9"/>
-      <c r="AI70" s="9"/>
-      <c r="AJ70" s="9"/>
-      <c r="AK70" s="9"/>
+      <c r="AI70" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="AJ70" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="AK70" s="19" t="s">
+        <v>338</v>
+      </c>
       <c r="AL70" s="9"/>
       <c r="AM70" s="9"/>
       <c r="AN70" s="9"/>
@@ -6118,10 +6211,10 @@
     <row r="71">
       <c r="A71" s="10"/>
       <c r="B71" s="84" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C71" s="84" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="D71" s="90"/>
       <c r="E71" s="14"/>
@@ -6164,10 +6257,10 @@
     <row r="72">
       <c r="A72" s="10"/>
       <c r="B72" s="84" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C72" s="84" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="D72" s="95"/>
       <c r="E72" s="14"/>
@@ -6210,13 +6303,13 @@
     <row r="73" ht="18.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="84" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C73" s="84" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="D73" s="97" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="E73" s="14" t="s">
         <v>55</v>
@@ -6225,7 +6318,7 @@
         <v>55</v>
       </c>
       <c r="G73" s="48" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="H73" s="14" t="s">
         <v>56</v>
@@ -6235,11 +6328,13 @@
         <v>55</v>
       </c>
       <c r="K73" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="L73" s="98"/>
+        <v>345</v>
+      </c>
+      <c r="L73" s="98" t="s">
+        <v>299</v>
+      </c>
       <c r="M73" s="12" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="N73" s="14" t="s">
         <v>55</v>
@@ -6247,22 +6342,22 @@
       <c r="O73" s="50"/>
       <c r="P73" s="50"/>
       <c r="Q73" s="12" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="R73" s="99" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="S73" s="99" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="T73" s="48" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="U73" s="48" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="V73" s="12" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="W73" s="14"/>
       <c r="X73" s="94"/>
@@ -6272,27 +6367,35 @@
       <c r="Z73" s="94"/>
       <c r="AA73" s="91"/>
       <c r="AB73" s="48" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="AC73" s="48" t="s">
-        <v>343</v>
-      </c>
-      <c r="AD73" s="98"/>
+        <v>354</v>
+      </c>
+      <c r="AD73" s="98" t="s">
+        <v>299</v>
+      </c>
       <c r="AE73" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="AF73" s="14" t="s">
-        <v>57</v>
+        <v>355</v>
+      </c>
+      <c r="AF73" s="12" t="s">
+        <v>356</v>
       </c>
       <c r="AG73" s="19" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="AH73" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="AI73" s="9"/>
-      <c r="AJ73" s="9"/>
-      <c r="AK73" s="9"/>
+        <v>358</v>
+      </c>
+      <c r="AI73" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="AJ73" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="AK73" s="19" t="s">
+        <v>361</v>
+      </c>
       <c r="AL73" s="9"/>
       <c r="AM73" s="9"/>
       <c r="AN73" s="9"/>
@@ -6300,13 +6403,13 @@
     <row r="74">
       <c r="A74" s="9"/>
       <c r="B74" s="18" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="E74" s="18" t="s">
         <v>55</v>
@@ -6315,7 +6418,7 @@
         <v>55</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="H74" s="18" t="s">
         <v>55</v>
@@ -6325,11 +6428,13 @@
         <v>55</v>
       </c>
       <c r="K74" s="19" t="s">
-        <v>350</v>
-      </c>
-      <c r="L74" s="18"/>
+        <v>365</v>
+      </c>
+      <c r="L74" s="18" t="s">
+        <v>299</v>
+      </c>
       <c r="M74" s="19" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="N74" s="18" t="s">
         <v>55</v>
@@ -6337,22 +6442,22 @@
       <c r="O74" s="9"/>
       <c r="P74" s="9"/>
       <c r="Q74" s="19" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="R74" s="19" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="S74" s="19" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="T74" s="19" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="U74" s="19" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="V74" s="19" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="W74" s="18" t="s">
         <v>57</v>
@@ -6371,14 +6476,20 @@
         <v>57</v>
       </c>
       <c r="AG74" s="19" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="AH74" s="19" t="s">
-        <v>359</v>
-      </c>
-      <c r="AI74" s="9"/>
-      <c r="AJ74" s="9"/>
-      <c r="AK74" s="9"/>
+        <v>374</v>
+      </c>
+      <c r="AI74" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="AJ74" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="AK74" s="19" t="s">
+        <v>377</v>
+      </c>
       <c r="AL74" s="9"/>
       <c r="AM74" s="9"/>
       <c r="AN74" s="9"/>
@@ -6386,13 +6497,13 @@
     <row r="75" ht="18.0" customHeight="1">
       <c r="A75" s="9"/>
       <c r="B75" s="18" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="E75" s="18" t="s">
         <v>55</v>
@@ -6401,7 +6512,7 @@
         <v>55</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="H75" s="18" t="s">
         <v>55</v>
@@ -6411,11 +6522,13 @@
         <v>55</v>
       </c>
       <c r="K75" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="L75" s="18"/>
+        <v>381</v>
+      </c>
+      <c r="L75" s="18" t="s">
+        <v>299</v>
+      </c>
       <c r="M75" s="19" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="N75" s="18" t="s">
         <v>55</v>
@@ -6423,19 +6536,19 @@
       <c r="O75" s="9"/>
       <c r="P75" s="9"/>
       <c r="Q75" s="19" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="R75" s="19" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="S75" s="19" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="T75" s="19" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="U75" s="19" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="V75" s="18" t="s">
         <v>56</v>
@@ -6450,27 +6563,35 @@
       <c r="Z75" s="9"/>
       <c r="AA75" s="9"/>
       <c r="AB75" s="19" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="AC75" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="AD75" s="18"/>
+        <v>389</v>
+      </c>
+      <c r="AD75" s="18" t="s">
+        <v>299</v>
+      </c>
       <c r="AE75" s="19" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="AF75" s="18" t="s">
         <v>57</v>
       </c>
       <c r="AG75" s="19" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="AH75" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="AI75" s="9"/>
-      <c r="AJ75" s="9"/>
-      <c r="AK75" s="9"/>
+        <v>392</v>
+      </c>
+      <c r="AI75" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="AJ75" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="AK75" s="19" t="s">
+        <v>395</v>
+      </c>
       <c r="AL75" s="9"/>
       <c r="AM75" s="9"/>
       <c r="AN75" s="9"/>
@@ -45503,88 +45624,108 @@
     <hyperlink r:id="rId174" ref="M59"/>
     <hyperlink r:id="rId175" ref="E60"/>
     <hyperlink r:id="rId176" ref="M61"/>
-    <hyperlink r:id="rId177" ref="V61"/>
-    <hyperlink r:id="rId178" ref="W61"/>
-    <hyperlink r:id="rId179" ref="AB61"/>
-    <hyperlink r:id="rId180" ref="AC61"/>
-    <hyperlink r:id="rId181" ref="AE61"/>
-    <hyperlink r:id="rId182" ref="N63"/>
-    <hyperlink r:id="rId183" ref="AB63"/>
-    <hyperlink r:id="rId184" ref="AC63"/>
-    <hyperlink r:id="rId185" ref="AE63"/>
-    <hyperlink r:id="rId186" ref="N65"/>
-    <hyperlink r:id="rId187" ref="O65"/>
-    <hyperlink r:id="rId188" ref="P65"/>
-    <hyperlink r:id="rId189" ref="Q65"/>
-    <hyperlink r:id="rId190" ref="N66"/>
-    <hyperlink r:id="rId191" ref="O66"/>
-    <hyperlink r:id="rId192" ref="P66"/>
-    <hyperlink r:id="rId193" ref="Q66"/>
-    <hyperlink r:id="rId194" ref="AB66"/>
-    <hyperlink r:id="rId195" ref="AC66"/>
-    <hyperlink r:id="rId196" ref="N67"/>
-    <hyperlink r:id="rId197" ref="O67"/>
-    <hyperlink r:id="rId198" ref="P67"/>
-    <hyperlink r:id="rId199" ref="Q67"/>
-    <hyperlink r:id="rId200" ref="D69"/>
-    <hyperlink r:id="rId201" ref="M69"/>
-    <hyperlink r:id="rId202" ref="V69"/>
-    <hyperlink r:id="rId203" ref="W69"/>
-    <hyperlink r:id="rId204" ref="Z69"/>
-    <hyperlink r:id="rId205" ref="AB69"/>
-    <hyperlink r:id="rId206" ref="AC69"/>
-    <hyperlink r:id="rId207" ref="AD69"/>
-    <hyperlink r:id="rId208" ref="AE69"/>
-    <hyperlink r:id="rId209" ref="D70"/>
-    <hyperlink r:id="rId210" ref="M70"/>
-    <hyperlink r:id="rId211" ref="V70"/>
-    <hyperlink r:id="rId212" ref="W70"/>
-    <hyperlink r:id="rId213" ref="Z70"/>
-    <hyperlink r:id="rId214" ref="AB70"/>
-    <hyperlink r:id="rId215" ref="AC70"/>
-    <hyperlink r:id="rId216" ref="AD70"/>
-    <hyperlink r:id="rId217" ref="D73"/>
-    <hyperlink r:id="rId218" ref="G73"/>
-    <hyperlink r:id="rId219" ref="K73"/>
-    <hyperlink r:id="rId220" ref="M73"/>
-    <hyperlink r:id="rId221" ref="Q73"/>
-    <hyperlink r:id="rId222" ref="R73"/>
-    <hyperlink r:id="rId223" ref="S73"/>
-    <hyperlink r:id="rId224" ref="T73"/>
-    <hyperlink r:id="rId225" ref="U73"/>
-    <hyperlink r:id="rId226" ref="V73"/>
-    <hyperlink r:id="rId227" ref="AB73"/>
-    <hyperlink r:id="rId228" ref="AC73"/>
-    <hyperlink r:id="rId229" ref="AE73"/>
-    <hyperlink r:id="rId230" ref="AG73"/>
-    <hyperlink r:id="rId231" ref="AH73"/>
-    <hyperlink r:id="rId232" ref="D74"/>
-    <hyperlink r:id="rId233" ref="G74"/>
-    <hyperlink r:id="rId234" ref="K74"/>
-    <hyperlink r:id="rId235" ref="M74"/>
-    <hyperlink r:id="rId236" ref="Q74"/>
-    <hyperlink r:id="rId237" ref="R74"/>
-    <hyperlink r:id="rId238" ref="S74"/>
-    <hyperlink r:id="rId239" ref="T74"/>
-    <hyperlink r:id="rId240" ref="U74"/>
-    <hyperlink r:id="rId241" ref="V74"/>
-    <hyperlink r:id="rId242" ref="AG74"/>
-    <hyperlink r:id="rId243" ref="AH74"/>
-    <hyperlink r:id="rId244" ref="D75"/>
-    <hyperlink r:id="rId245" ref="G75"/>
-    <hyperlink r:id="rId246" ref="K75"/>
-    <hyperlink r:id="rId247" ref="M75"/>
-    <hyperlink r:id="rId248" ref="Q75"/>
-    <hyperlink r:id="rId249" ref="R75"/>
-    <hyperlink r:id="rId250" ref="S75"/>
-    <hyperlink r:id="rId251" ref="T75"/>
-    <hyperlink r:id="rId252" ref="U75"/>
-    <hyperlink r:id="rId253" ref="AB75"/>
-    <hyperlink r:id="rId254" ref="AC75"/>
-    <hyperlink r:id="rId255" ref="AE75"/>
-    <hyperlink r:id="rId256" ref="AG75"/>
-    <hyperlink r:id="rId257" ref="AH75"/>
+    <hyperlink r:id="rId177" ref="N61"/>
+    <hyperlink r:id="rId178" ref="V61"/>
+    <hyperlink r:id="rId179" ref="W61"/>
+    <hyperlink r:id="rId180" ref="AB61"/>
+    <hyperlink r:id="rId181" ref="AC61"/>
+    <hyperlink r:id="rId182" ref="AE61"/>
+    <hyperlink r:id="rId183" ref="N63"/>
+    <hyperlink r:id="rId184" ref="AB63"/>
+    <hyperlink r:id="rId185" ref="AC63"/>
+    <hyperlink r:id="rId186" ref="AE63"/>
+    <hyperlink r:id="rId187" ref="AI63"/>
+    <hyperlink r:id="rId188" ref="AJ63"/>
+    <hyperlink r:id="rId189" ref="AK63"/>
+    <hyperlink r:id="rId190" ref="N65"/>
+    <hyperlink r:id="rId191" ref="O65"/>
+    <hyperlink r:id="rId192" ref="P65"/>
+    <hyperlink r:id="rId193" ref="Q65"/>
+    <hyperlink r:id="rId194" ref="N66"/>
+    <hyperlink r:id="rId195" ref="O66"/>
+    <hyperlink r:id="rId196" ref="P66"/>
+    <hyperlink r:id="rId197" ref="Q66"/>
+    <hyperlink r:id="rId198" ref="AB66"/>
+    <hyperlink r:id="rId199" ref="AC66"/>
+    <hyperlink r:id="rId200" ref="N67"/>
+    <hyperlink r:id="rId201" ref="O67"/>
+    <hyperlink r:id="rId202" ref="P67"/>
+    <hyperlink r:id="rId203" ref="Q67"/>
+    <hyperlink r:id="rId204" ref="D69"/>
+    <hyperlink r:id="rId205" ref="M69"/>
+    <hyperlink r:id="rId206" ref="V69"/>
+    <hyperlink r:id="rId207" ref="W69"/>
+    <hyperlink r:id="rId208" ref="Z69"/>
+    <hyperlink r:id="rId209" ref="AB69"/>
+    <hyperlink r:id="rId210" ref="AC69"/>
+    <hyperlink r:id="rId211" ref="AD69"/>
+    <hyperlink r:id="rId212" ref="AE69"/>
+    <hyperlink r:id="rId213" ref="AI69"/>
+    <hyperlink r:id="rId214" ref="AJ69"/>
+    <hyperlink r:id="rId215" ref="AK69"/>
+    <hyperlink r:id="rId216" ref="D70"/>
+    <hyperlink r:id="rId217" ref="M70"/>
+    <hyperlink r:id="rId218" ref="V70"/>
+    <hyperlink r:id="rId219" ref="W70"/>
+    <hyperlink r:id="rId220" ref="Z70"/>
+    <hyperlink r:id="rId221" ref="AB70"/>
+    <hyperlink r:id="rId222" ref="AC70"/>
+    <hyperlink r:id="rId223" ref="AD70"/>
+    <hyperlink r:id="rId224" ref="AI70"/>
+    <hyperlink r:id="rId225" ref="AJ70"/>
+    <hyperlink r:id="rId226" ref="AK70"/>
+    <hyperlink r:id="rId227" ref="D73"/>
+    <hyperlink r:id="rId228" ref="G73"/>
+    <hyperlink r:id="rId229" ref="K73"/>
+    <hyperlink r:id="rId230" ref="M73"/>
+    <hyperlink r:id="rId231" ref="Q73"/>
+    <hyperlink r:id="rId232" ref="R73"/>
+    <hyperlink r:id="rId233" ref="S73"/>
+    <hyperlink r:id="rId234" ref="T73"/>
+    <hyperlink r:id="rId235" ref="U73"/>
+    <hyperlink r:id="rId236" ref="V73"/>
+    <hyperlink r:id="rId237" ref="AB73"/>
+    <hyperlink r:id="rId238" ref="AC73"/>
+    <hyperlink r:id="rId239" ref="AE73"/>
+    <hyperlink r:id="rId240" ref="AF73"/>
+    <hyperlink r:id="rId241" ref="AG73"/>
+    <hyperlink r:id="rId242" ref="AH73"/>
+    <hyperlink r:id="rId243" ref="AI73"/>
+    <hyperlink r:id="rId244" ref="AJ73"/>
+    <hyperlink r:id="rId245" ref="AK73"/>
+    <hyperlink r:id="rId246" ref="D74"/>
+    <hyperlink r:id="rId247" ref="G74"/>
+    <hyperlink r:id="rId248" ref="K74"/>
+    <hyperlink r:id="rId249" ref="M74"/>
+    <hyperlink r:id="rId250" ref="Q74"/>
+    <hyperlink r:id="rId251" ref="R74"/>
+    <hyperlink r:id="rId252" ref="S74"/>
+    <hyperlink r:id="rId253" ref="T74"/>
+    <hyperlink r:id="rId254" ref="U74"/>
+    <hyperlink r:id="rId255" ref="V74"/>
+    <hyperlink r:id="rId256" ref="AG74"/>
+    <hyperlink r:id="rId257" ref="AH74"/>
+    <hyperlink r:id="rId258" ref="AI74"/>
+    <hyperlink r:id="rId259" ref="AJ74"/>
+    <hyperlink r:id="rId260" ref="AK74"/>
+    <hyperlink r:id="rId261" ref="D75"/>
+    <hyperlink r:id="rId262" ref="G75"/>
+    <hyperlink r:id="rId263" ref="K75"/>
+    <hyperlink r:id="rId264" ref="M75"/>
+    <hyperlink r:id="rId265" ref="Q75"/>
+    <hyperlink r:id="rId266" ref="R75"/>
+    <hyperlink r:id="rId267" ref="S75"/>
+    <hyperlink r:id="rId268" ref="T75"/>
+    <hyperlink r:id="rId269" ref="U75"/>
+    <hyperlink r:id="rId270" ref="AB75"/>
+    <hyperlink r:id="rId271" ref="AC75"/>
+    <hyperlink r:id="rId272" ref="AE75"/>
+    <hyperlink r:id="rId273" ref="AG75"/>
+    <hyperlink r:id="rId274" ref="AH75"/>
+    <hyperlink r:id="rId275" ref="AI75"/>
+    <hyperlink r:id="rId276" ref="AJ75"/>
+    <hyperlink r:id="rId277" ref="AK75"/>
   </hyperlinks>
-  <drawing r:id="rId258"/>
+  <drawing r:id="rId278"/>
 </worksheet>
 </file>